--- a/data/rete_ftth_collesalvetti.xlsx
+++ b/data/rete_ftth_collesalvetti.xlsx
@@ -1,9 +1,9 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Rete FTTH Collesalvetti" sheetId="1" r:id="rId1"/>
-  </sheets>
+    <sheets>
+        <sheet name="Rete FTTH & Cantieri" sheetId="1" r:id="rId1"/>
+    </sheets>
 </workbook>
 </file>
 
@@ -83,47 +83,72 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Stato / Attivazione Cantiere</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Periodo Lavori (Inizio - Fine)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Vie Coinvolte</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Riferimento Ordinanza Comunale</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Latitudine</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Longitudine</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Quota (m s.l.m.)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lunghezza (m)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Lunghezza (km)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Superficie (m²)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Superficie (km²)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Note Tecniche e Dettagli sul Campo</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Link Google Maps</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Link Ordinanza PDF</t>
         </is>
       </c>
     </row>
@@ -140,7 +165,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -153,21 +178,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J2">
         <v>43.591353</v>
       </c>
-      <c r="G2">
+      <c r="K2">
         <v>10.473372</v>
       </c>
-      <c r="I2">
+      <c r="M2">
         <v>1096.2</v>
       </c>
-      <c r="J2">
+      <c r="N2">
         <v>1.096</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591353,10.473372</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -184,7 +239,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -197,21 +252,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J3">
         <v>43.595559</v>
       </c>
-      <c r="G3">
+      <c r="K3">
         <v>10.477378</v>
       </c>
-      <c r="I3">
+      <c r="M3">
         <v>325.2</v>
       </c>
-      <c r="J3">
+      <c r="N3">
         <v>0.325</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.595559,10.477378</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -241,21 +326,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="J4">
         <v>43.595685</v>
       </c>
-      <c r="G4">
+      <c r="K4">
         <v>10.474887</v>
       </c>
-      <c r="H4">
+      <c r="L4">
         <v>14.3</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione | Apparato supplementare | Tombini Telecom e TIM vicini</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.595685,10.474887</t>
         </is>
@@ -287,21 +372,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="J5">
         <v>43.591096</v>
       </c>
-      <c r="G5">
+      <c r="K5">
         <v>10.475529</v>
       </c>
-      <c r="H5">
+      <c r="L5">
         <v>25.8</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione | Apparato aggiuntivo | Tombino Telecom datato</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591096,10.475529</t>
         </is>
@@ -333,21 +418,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="J6">
         <v>43.588583</v>
       </c>
-      <c r="G6">
+      <c r="K6">
         <v>10.473953</v>
       </c>
-      <c r="H6">
+      <c r="L6">
         <v>21.4</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Solo ARL</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.588583,10.473953</t>
         </is>
@@ -379,21 +464,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="J7">
         <v>43.588526</v>
       </c>
-      <c r="G7">
+      <c r="K7">
         <v>10.472213</v>
       </c>
-      <c r="H7">
+      <c r="L7">
         <v>23.0</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Solo ARL</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.588526,10.472213</t>
         </is>
@@ -425,21 +510,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="J8">
         <v>43.58851</v>
       </c>
-      <c r="G8">
+      <c r="K8">
         <v>10.47337</v>
       </c>
-      <c r="H8">
+      <c r="L8">
         <v>26.4</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.58851,10.47337</t>
         </is>
@@ -471,21 +556,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="J9">
         <v>43.593381</v>
       </c>
-      <c r="G9">
+      <c r="K9">
         <v>10.471502</v>
       </c>
-      <c r="H9">
+      <c r="L9">
         <v>13.0</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.593381,10.471502</t>
         </is>
@@ -517,21 +602,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="J10">
         <v>43.587389</v>
       </c>
-      <c r="G10">
+      <c r="K10">
         <v>10.476109</v>
       </c>
-      <c r="H10">
+      <c r="L10">
         <v>47.0</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Solo ARL | NUMERO DA VERIFICARE IRL</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.587389,10.476109</t>
         </is>
@@ -563,21 +648,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="J11">
         <v>43.615979</v>
       </c>
-      <c r="G11">
+      <c r="K11">
         <v>10.463939</v>
       </c>
-      <c r="H11">
+      <c r="L11">
         <v>8.9</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Piccolo apparato e-distribuzione appeso allo SLAM</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.615979,10.463939</t>
         </is>
@@ -609,21 +694,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="J12">
         <v>43.614158</v>
       </c>
-      <c r="G12">
+      <c r="K12">
         <v>10.464706</v>
       </c>
-      <c r="H12">
+      <c r="L12">
         <v>8.3</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione | Apparato aggiuntivo | Tombini TIM e INWIT</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.614158,10.464706</t>
         </is>
@@ -655,21 +740,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="J13">
         <v>43.611401</v>
       </c>
-      <c r="G13">
+      <c r="K13">
         <v>10.462766</v>
       </c>
-      <c r="H13">
+      <c r="L13">
         <v>7.2</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.611401,10.462766</t>
         </is>
@@ -701,21 +786,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="J14">
         <v>43.611423</v>
       </c>
-      <c r="G14">
+      <c r="K14">
         <v>10.467038</v>
       </c>
-      <c r="H14">
+      <c r="L14">
         <v>9.4</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.611423,10.467038</t>
         </is>
@@ -747,21 +832,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="J15">
         <v>43.608954</v>
       </c>
-      <c r="G15">
+      <c r="K15">
         <v>10.468205</v>
       </c>
-      <c r="H15">
+      <c r="L15">
         <v>9.9</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Solo ARL | NUOVO DAL 2025</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.608954,10.468205</t>
         </is>
@@ -793,21 +878,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="J16">
         <v>43.607712</v>
       </c>
-      <c r="G16">
+      <c r="K16">
         <v>10.469103</v>
       </c>
-      <c r="H16">
+      <c r="L16">
         <v>20.1</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.607712,10.469103</t>
         </is>
@@ -839,21 +924,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="J17">
         <v>43.60849</v>
       </c>
-      <c r="G17">
+      <c r="K17">
         <v>10.459436</v>
       </c>
-      <c r="H17">
+      <c r="L17">
         <v>8.1</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.60849,10.459436</t>
         </is>
@@ -885,21 +970,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="J18">
         <v>43.605143</v>
       </c>
-      <c r="G18">
+      <c r="K18">
         <v>10.440451</v>
       </c>
-      <c r="H18">
+      <c r="L18">
         <v>6.2</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.605143,10.440451</t>
         </is>
@@ -931,16 +1016,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="J19">
         <v>43.590687</v>
       </c>
-      <c r="G19">
+      <c r="K19">
         <v>10.35622</v>
       </c>
-      <c r="H19">
+      <c r="L19">
         <v>9.2</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.590687,10.35622</t>
         </is>
@@ -972,21 +1057,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="J20">
         <v>43.592438</v>
       </c>
-      <c r="G20">
+      <c r="K20">
         <v>10.350568</v>
       </c>
-      <c r="H20">
+      <c r="L20">
         <v>2.5</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Con apparato aggiuntivo</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.592438,10.350568</t>
         </is>
@@ -1018,21 +1103,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="J21">
         <v>43.589338</v>
       </c>
-      <c r="G21">
+      <c r="K21">
         <v>10.353907</v>
       </c>
-      <c r="H21">
+      <c r="L21">
         <v>5.4</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.589338,10.353907</t>
         </is>
@@ -1064,21 +1149,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="J22">
         <v>43.590359</v>
       </c>
-      <c r="G22">
+      <c r="K22">
         <v>10.353377</v>
       </c>
-      <c r="H22">
+      <c r="L22">
         <v>12.5</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Solo ARL</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.590359,10.353377</t>
         </is>
@@ -1110,21 +1195,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="J23">
         <v>43.589462</v>
       </c>
-      <c r="G23">
+      <c r="K23">
         <v>10.349117</v>
       </c>
-      <c r="H23">
+      <c r="L23">
         <v>2.7</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Solo ARL</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.589462,10.349117</t>
         </is>
@@ -1156,16 +1241,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="J24">
         <v>43.591341</v>
       </c>
-      <c r="G24">
+      <c r="K24">
         <v>10.350005</v>
       </c>
-      <c r="H24">
+      <c r="L24">
         <v>2.4</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591341,10.350005</t>
         </is>
@@ -1197,21 +1282,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="J25">
         <v>43.597713</v>
       </c>
-      <c r="G25">
+      <c r="K25">
         <v>10.408314</v>
       </c>
-      <c r="H25">
+      <c r="L25">
         <v>4.3</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Solo ARL | Tombini TIM vicini</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.597713,10.408314</t>
         </is>
@@ -1243,21 +1328,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="J26">
         <v>43.597372</v>
       </c>
-      <c r="G26">
+      <c r="K26">
         <v>10.405911</v>
       </c>
-      <c r="H26">
+      <c r="L26">
         <v>4.9</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Colonnina e-distribuzione</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.597372,10.405911</t>
         </is>
@@ -1289,21 +1374,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="J27">
         <v>43.59665</v>
       </c>
-      <c r="G27">
+      <c r="K27">
         <v>10.391757</v>
       </c>
-      <c r="H27">
+      <c r="L27">
         <v>2.8</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Alimentazione e-distribuzione appesa allo SLAM | Da verificare numero IRL</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.59665,10.391757</t>
         </is>
@@ -1335,21 +1420,21 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="J28">
         <v>43.587841</v>
       </c>
-      <c r="G28">
+      <c r="K28">
         <v>10.477201</v>
       </c>
-      <c r="H28">
+      <c r="L28">
         <v>47.5</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>XGS-PON (10 gigabit) | Tombini Telecom, TIM e Fastweb (quest'ultimo per allacciare Casa di Riposo Santa Caterina)</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.587841,10.477201</t>
         </is>
@@ -1381,16 +1466,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="J29">
         <v>43.608339</v>
       </c>
-      <c r="G29">
+      <c r="K29">
         <v>10.471259</v>
       </c>
-      <c r="H29">
+      <c r="L29">
         <v>17.1</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.608339,10.471259</t>
         </is>
@@ -1422,16 +1507,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="J30">
         <v>43.596228</v>
       </c>
-      <c r="G30">
+      <c r="K30">
         <v>10.406849</v>
       </c>
-      <c r="H30">
+      <c r="L30">
         <v>8.2</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.596228,10.406849</t>
         </is>
@@ -1463,16 +1548,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="J31">
         <v>43.577525</v>
       </c>
-      <c r="G31">
+      <c r="K31">
         <v>10.438356</v>
       </c>
-      <c r="H31">
+      <c r="L31">
         <v>67.0</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.577525,10.438356</t>
         </is>
@@ -1504,16 +1589,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="J32">
         <v>43.538167</v>
       </c>
-      <c r="G32">
+      <c r="K32">
         <v>10.442333</v>
       </c>
-      <c r="H32">
+      <c r="L32">
         <v>0.0</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.538167,10.442333</t>
         </is>
@@ -1545,16 +1630,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="J33">
         <v>43.528528</v>
       </c>
-      <c r="G33">
+      <c r="K33">
         <v>10.457333</v>
       </c>
-      <c r="H33">
+      <c r="L33">
         <v>0.0</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.528528,10.457333</t>
         </is>
@@ -1586,16 +1671,16 @@
           <t>Point</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="J34">
         <v>43.586222</v>
       </c>
-      <c r="G34">
+      <c r="K34">
         <v>10.347222</v>
       </c>
-      <c r="H34">
+      <c r="L34">
         <v>0.0</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.586222,10.347222</t>
         </is>
@@ -1627,19 +1712,19 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="J35">
         <v>43.591686</v>
       </c>
-      <c r="G35">
+      <c r="K35">
         <v>10.348608</v>
       </c>
-      <c r="I35">
+      <c r="M35">
         <v>1833.4</v>
       </c>
-      <c r="J35">
+      <c r="N35">
         <v>1.833</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591686,10.348608</t>
         </is>
@@ -1671,19 +1756,19 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="J36">
         <v>43.594286</v>
       </c>
-      <c r="G36">
+      <c r="K36">
         <v>10.351331</v>
       </c>
-      <c r="I36">
+      <c r="M36">
         <v>346.9</v>
       </c>
-      <c r="J36">
+      <c r="N36">
         <v>0.347</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.594286,10.351331</t>
         </is>
@@ -1715,24 +1800,24 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="J37">
         <v>43.596264</v>
       </c>
-      <c r="G37">
+      <c r="K37">
         <v>10.406675</v>
       </c>
-      <c r="I37">
+      <c r="M37">
         <v>6533.3</v>
       </c>
-      <c r="J37">
+      <c r="N37">
         <v>6.533</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>TORSFNUGOLANUOVA | Un percorso con un misto di palifica, cavidotto e mini trincea per rilegare in fibra ottica le centrali Fibercop usando il progetto del MISR 2014-2020</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.596264,10.406675</t>
         </is>
@@ -1751,7 +1836,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1764,21 +1849,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J38">
         <v>43.593705</v>
       </c>
-      <c r="G38">
+      <c r="K38">
         <v>10.474944</v>
       </c>
-      <c r="I38">
+      <c r="M38">
         <v>96.5</v>
       </c>
-      <c r="J38">
+      <c r="N38">
         <v>0.097</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.593705,10.474944</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1910,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1808,21 +1923,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J39">
         <v>43.592936</v>
       </c>
-      <c r="G39">
+      <c r="K39">
         <v>10.47365</v>
       </c>
-      <c r="I39">
+      <c r="M39">
         <v>513.7</v>
       </c>
-      <c r="J39">
+      <c r="N39">
         <v>0.514</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.592936,10.47365</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1984,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1852,21 +1997,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J40">
         <v>43.593821</v>
       </c>
-      <c r="G40">
+      <c r="K40">
         <v>10.475403</v>
       </c>
-      <c r="I40">
+      <c r="M40">
         <v>293.4</v>
       </c>
-      <c r="J40">
+      <c r="N40">
         <v>0.293</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.593821,10.475403</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -1883,7 +2058,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cantiere Fibra Ottica</t>
+          <t>Cantiere FTTH (Attivazione Imminente)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1896,21 +2071,51 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>IMMINENTE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-09-14 -&gt; 2026-10-02</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Via Nenni, Via Roma (rotatoria Via Nenni), Via del Valico a Pisa, Via di Cerretello</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 88 del 02/09/2026 (Reg. Gen. 95)</t>
+        </is>
+      </c>
+      <c r="J41">
         <v>43.593354</v>
       </c>
-      <c r="G41">
+      <c r="K41">
         <v>10.477089</v>
       </c>
-      <c r="I41">
+      <c r="M41">
         <v>340.9</v>
       </c>
-      <c r="J41">
+      <c r="N41">
         <v>0.341</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH FiberCop Collesalvetti (Ord. 95/2026 del 02/09/2026). Vie: Via Nenni, Via Roma, Via del Valico a Pisa, Via di Cerretello.</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.593354,10.477089</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_95_2026_collesalvetti_cantiere1.pdf</t>
         </is>
       </c>
     </row>
@@ -1940,19 +2145,19 @@
           <t>Polygon</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="J42">
         <v>43.597352</v>
       </c>
-      <c r="G42">
+      <c r="K42">
         <v>10.478314</v>
       </c>
-      <c r="K42">
+      <c r="O42">
         <v>205512.9</v>
       </c>
-      <c r="L42">
+      <c r="P42">
         <v>0.2055</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.597352,10.478314</t>
         </is>
@@ -1984,19 +2189,19 @@
           <t>Polygon</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="J43">
         <v>43.591043</v>
       </c>
-      <c r="G43">
+      <c r="K43">
         <v>10.471834</v>
       </c>
-      <c r="K43">
+      <c r="O43">
         <v>455950.0</v>
       </c>
-      <c r="L43">
+      <c r="P43">
         <v>0.456</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591043,10.471834</t>
         </is>
@@ -2028,24 +2233,24 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="J44">
         <v>43.595701</v>
       </c>
-      <c r="G44">
+      <c r="K44">
         <v>10.474857</v>
       </c>
-      <c r="I44">
+      <c r="M44">
         <v>345.6</v>
       </c>
-      <c r="J44">
+      <c r="N44">
         <v>0.346</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Realizzato nel 2025-2026, una decina di pozzetti marchio Fibercop (logo nuovo). Collega ARL 01 a Scuole medie e la nuova struttura di asilo nido "I cubi". Hanno fatto delle mini-trincee</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.595701,10.474857</t>
         </is>
@@ -2077,24 +2282,24 @@
           <t>LineString</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="J45">
         <v>43.587826</v>
       </c>
-      <c r="G45">
+      <c r="K45">
         <v>10.477238</v>
       </c>
-      <c r="I45">
+      <c r="M45">
         <v>348.3</v>
       </c>
-      <c r="J45">
+      <c r="N45">
         <v>0.348</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Realizzato nel 2026. Scavo per conto di Fastweb che ha vinto il bando per connettere le strutture sanitarie nel comune. Pozzetti Fastweb e mini-trincee. Collega la centrale Fibercop a Casa di Riposo Santa Caterina e USL Collesalvetti.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.587826,10.477238</t>
         </is>
@@ -2126,19 +2331,19 @@
           <t>Polygon</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="J46">
         <v>43.591561</v>
       </c>
-      <c r="G46">
+      <c r="K46">
         <v>10.348533</v>
       </c>
-      <c r="K46">
-        <v>286535.2</v>
-      </c>
-      <c r="L46">
-        <v>0.2865</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46">
+        <v>371709.9</v>
+      </c>
+      <c r="P46">
+        <v>0.3717</v>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.591561,10.348533</t>
         </is>
@@ -2170,21 +2375,243 @@
           <t>Polygon</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="J47">
         <v>43.589887</v>
       </c>
-      <c r="G47">
+      <c r="K47">
         <v>10.347674</v>
       </c>
-      <c r="K47">
-        <v>172854.7</v>
-      </c>
-      <c r="L47">
-        <v>0.1729</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47">
+        <v>91283.7</v>
+      </c>
+      <c r="P47">
+        <v>0.0913</v>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>https://www.google.com/maps?q=43.589887,10.347674</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0AD5AAF68741C10071CC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cantiere 2 (21/09-16/10)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH (Nuova Ordinanza Programmata)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Stagno</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PROGRAMMATO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-09-21 -&gt; 2026-10-16</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 95 del 10/09/2026 (Reg. Gen. 102)</t>
+        </is>
+      </c>
+      <c r="J48">
+        <v>43.590227</v>
+      </c>
+      <c r="K48">
+        <v>10.353891</v>
+      </c>
+      <c r="M48">
+        <v>792.4</v>
+      </c>
+      <c r="N48">
+        <v>0.792</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Nuovo cantiere FTTH FiberCop Stagno (Ord. 102/2026 del 10/09/2026). Vie: Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio.</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=43.590227,10.353891</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_102_2026_stagno_cantiere2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>04D8D17C9141C10125EB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cantiere 2 (21/09-16/10)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH (Nuova Ordinanza Programmata)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Stagno</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PROGRAMMATO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-09-21 -&gt; 2026-10-16</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 95 del 10/09/2026 (Reg. Gen. 102)</t>
+        </is>
+      </c>
+      <c r="J49">
+        <v>43.590159</v>
+      </c>
+      <c r="K49">
+        <v>10.353883</v>
+      </c>
+      <c r="M49">
+        <v>360.5</v>
+      </c>
+      <c r="N49">
+        <v>0.36</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Nuovo cantiere FTTH FiberCop Stagno (Ord. 102/2026 del 10/09/2026). Vie: Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio.</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=43.590159,10.353883</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_102_2026_stagno_cantiere2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>01393CA83D41C1030753</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cantiere 2 (21/09-16/10)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cantiere FTTH (Nuova Ordinanza Programmata)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Stagno</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LineString</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PROGRAMMATO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-09-21 -&gt; 2026-10-16</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ordinanza P.M. n. 95 del 10/09/2026 (Reg. Gen. 102)</t>
+        </is>
+      </c>
+      <c r="J50">
+        <v>43.588516</v>
+      </c>
+      <c r="K50">
+        <v>10.353942</v>
+      </c>
+      <c r="M50">
+        <v>277.9</v>
+      </c>
+      <c r="N50">
+        <v>0.278</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Nuovo cantiere FTTH FiberCop Stagno (Ord. 102/2026 del 10/09/2026). Vie: Via Otto Marzo, Via Romita, Via De Gasperi, Via Machiavelli, Via XXV Aprile, Piazza Di Vittorio.</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=43.588516,10.353942</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>ordinanze/ordinanza_102_2026_stagno_cantiere2.pdf</t>
         </is>
       </c>
     </row>
